--- a/data/sars/atlantic/tables/Atlantic_1996_Appendix1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_1996_Appendix1.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E31675D-3520-E24D-9520-7280293077C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8123392-1F04-E94A-A065-29E6ADB25AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="500" windowWidth="25860" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="500" windowWidth="28960" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$K$58</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="68">
   <si>
     <t>Harbor seal</t>
   </si>
@@ -122,162 +125,6 @@
   </si>
   <si>
     <t>Bryde's whale</t>
-  </si>
-  <si>
-    <r>
-      <t>1,617</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>8,794</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4,968</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10,11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>11,12</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>11</t>
-    </r>
   </si>
   <si>
     <t>species</t>
@@ -390,7 +237,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -410,18 +257,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -447,48 +282,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -798,7 +636,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="50.796875" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="44.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.19921875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.59765625" style="4" customWidth="1"/>
     <col min="3" max="3" width="8.19921875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="8" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.796875" style="4" bestFit="1" customWidth="1"/>
@@ -812,37 +650,37 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="K1" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="L1" s="3"/>
     </row>
@@ -851,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>1</v>
@@ -887,7 +725,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>1</v>
@@ -923,7 +761,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>1</v>
@@ -959,7 +797,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>1</v>
@@ -995,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>1</v>
@@ -1031,7 +869,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>1</v>
@@ -1063,10 +901,10 @@
     </row>
     <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>1</v>
@@ -1102,7 +940,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>1</v>
@@ -1137,7 +975,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>1</v>
@@ -1168,12 +1006,12 @@
       </c>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>1</v>
@@ -1181,8 +1019,8 @@
       <c r="D11" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>34</v>
+      <c r="E11" s="14">
+        <v>1617</v>
       </c>
       <c r="F11" s="9">
         <v>0.04</v>
@@ -1204,12 +1042,12 @@
       </c>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>1</v>
@@ -1217,8 +1055,8 @@
       <c r="D12" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>34</v>
+      <c r="E12" s="14">
+        <v>1617</v>
       </c>
       <c r="F12" s="9">
         <v>0.04</v>
@@ -1244,7 +1082,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>1</v>
@@ -1279,7 +1117,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>1</v>
@@ -1309,12 +1147,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>1</v>
@@ -1322,8 +1160,8 @@
       <c r="D15" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>35</v>
+      <c r="E15" s="14">
+        <v>8794</v>
       </c>
       <c r="F15" s="9">
         <v>0.04</v>
@@ -1350,7 +1188,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>1</v>
@@ -1386,7 +1224,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>1</v>
@@ -1422,7 +1260,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>1</v>
@@ -1457,7 +1295,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>1</v>
@@ -1493,7 +1331,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>1</v>
@@ -1525,10 +1363,10 @@
     </row>
     <row r="21" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>1</v>
@@ -1563,7 +1401,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>1</v>
@@ -1596,10 +1434,10 @@
     </row>
     <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>1</v>
@@ -1629,12 +1467,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="7" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>1</v>
@@ -1642,8 +1480,8 @@
       <c r="D24" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>36</v>
+      <c r="E24" s="14">
+        <v>4968</v>
       </c>
       <c r="F24" s="9">
         <v>0.04</v>
@@ -1660,16 +1498,16 @@
       <c r="J24" s="11">
         <v>426</v>
       </c>
-      <c r="K24" s="12" t="s">
-        <v>37</v>
+      <c r="K24" s="7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>1</v>
@@ -1704,7 +1542,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>1</v>
@@ -1736,10 +1574,10 @@
     </row>
     <row r="27" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="7" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>1</v>
@@ -1774,7 +1612,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>1</v>
@@ -1810,7 +1648,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>1</v>
@@ -1846,7 +1684,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>1</v>
@@ -1881,7 +1719,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>1</v>
@@ -1916,7 +1754,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>1</v>
@@ -1947,12 +1785,12 @@
       </c>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" spans="1:12" ht="30" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>1</v>
@@ -1983,12 +1821,12 @@
       </c>
       <c r="L33" s="5"/>
     </row>
-    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>1</v>
@@ -2011,20 +1849,20 @@
       <c r="I34" s="10">
         <v>2.8</v>
       </c>
-      <c r="J34" s="12" t="s">
-        <v>38</v>
+      <c r="J34" s="12">
+        <v>2.8</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>3</v>
       </c>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>1</v>
@@ -2047,20 +1885,20 @@
       <c r="I35" s="11">
         <v>13</v>
       </c>
-      <c r="J35" s="12" t="s">
-        <v>39</v>
+      <c r="J35" s="12">
+        <v>13</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>3</v>
       </c>
       <c r="L35" s="5"/>
     </row>
-    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>1</v>
@@ -2083,20 +1921,20 @@
       <c r="I36" s="11">
         <v>10</v>
       </c>
-      <c r="J36" s="12" t="s">
-        <v>40</v>
+      <c r="J36" s="12">
+        <v>10</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>3</v>
       </c>
       <c r="L36" s="5"/>
     </row>
-    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>1</v>
@@ -2119,20 +1957,20 @@
       <c r="I37" s="11">
         <v>8</v>
       </c>
-      <c r="J37" s="12" t="s">
-        <v>41</v>
+      <c r="J37" s="12">
+        <v>8</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>3</v>
       </c>
       <c r="L37" s="5"/>
     </row>
-    <row r="38" spans="1:12" ht="30" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>1</v>
@@ -2155,8 +1993,8 @@
       <c r="I38" s="11">
         <v>30</v>
       </c>
-      <c r="J38" s="12" t="s">
-        <v>42</v>
+      <c r="J38" s="12">
+        <v>30</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>9</v>
@@ -2165,10 +2003,10 @@
     </row>
     <row r="39" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>1</v>
@@ -2201,10 +2039,10 @@
     </row>
     <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>1</v>
@@ -2239,7 +2077,7 @@
         <v>13</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>1</v>
@@ -2274,7 +2112,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>1</v>
@@ -2306,10 +2144,10 @@
     </row>
     <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>1</v>
@@ -2344,7 +2182,7 @@
         <v>28</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>1</v>
@@ -2380,7 +2218,7 @@
         <v>29</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>1</v>
@@ -2416,7 +2254,7 @@
         <v>19</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>1</v>
@@ -2452,7 +2290,7 @@
         <v>30</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>1</v>
@@ -2488,7 +2326,7 @@
         <v>20</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>1</v>
@@ -2523,7 +2361,7 @@
         <v>17</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>1</v>
@@ -2559,7 +2397,7 @@
         <v>18</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>1</v>
@@ -2594,7 +2432,7 @@
         <v>31</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>1</v>
@@ -2630,7 +2468,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>1</v>
@@ -2665,7 +2503,7 @@
         <v>21</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>1</v>
@@ -2698,10 +2536,10 @@
     </row>
     <row r="54" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="7" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>1</v>
@@ -2737,7 +2575,7 @@
         <v>32</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>1</v>
@@ -2770,10 +2608,10 @@
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>1</v>
@@ -2808,7 +2646,7 @@
         <v>22</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>1</v>
@@ -2843,7 +2681,7 @@
         <v>33</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>1</v>
@@ -3808,6 +3646,7 @@
       <c r="L129" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K58" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>